--- a/output/客戶名單_177家.xlsx
+++ b/output/客戶名單_177家.xlsx
@@ -442,1999 +442,2370 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>公司名稱</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>永續報告書超連結網址</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>客戶部門</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>客戶職稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>客戶姓氏</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>客戶姓名</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>信箱</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>成霖企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://tw.globeunion.com/sustainability/sustainable-development/esg-reports/</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>黃</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>黃曉惠</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ann.huang@globeunion.com</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>(886)-4-25349676</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TPK Holding Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://www.tpk.com/</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>esg@tpk.com</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>幸福水泥股份有限公司</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>https://www.luckygrp.com.tw/luckygrp/CorporateSustainabilityReport</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>品保中心</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>welson@luckygrp.com.tw</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>02-25092188#2326</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>磐亞股份有限公司</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>https://www.pacc.com.tw/social_tw.php?id=4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>永續發展推動小組</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>4707pacc@pacc.com.tw</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>(02) 2351-1212</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>宏遠證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>https://www.honsec.com.tw/about/?l=3&amp;id=1088</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>victoria.wang@honsec.com.tw</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>三芳化學工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>https://www.sanfang.com/zh/sustainability/</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>jui@sanfang.com.tw; smf@sanfang.com.tw</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>台達化學工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>https://www.ttc.com.tw/zh-tw/dirCSRnew/frmReport.aspx</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>鍾</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>鍾先生</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>esg-ttc@usig.com</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>+886 7 7040988 分機 1343</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>敬鵬工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>https://www.chinpoon.com/archive/sustainability/item/PDF/SustainabilityReport/2023%20Sustainability%20Report.pdf</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>spokesman@tw.chinpoon.com</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>+886-3-322-2226</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>漢磊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>https://www.episil.com/zh-tw/esg/esg_download</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>episil_mail@episil.com</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>03-5779245</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>龍邦國際興業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>http://www.longbon.com.tw/%e4%bc%81%e6%a5%ad%e6%b0%b8%e7%ba%8c/%e6%b0%b8%e7%ba%8c%e5%a0%b1%e5%91%8a%e6%9b%b8/</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>esg@longbon.com.tw</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>02-2375-6595</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>奇鋐科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>https://www.avc.co/zh-tw/CorporateResponsibility/CorporateCSR</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>永續發展暨風險管理委員會</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>esg@avc.co</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>巨大機械工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>https://www.giantgroup-cycling.com/esg/reportpage</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>esg@giant.com.tw</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>中光電投資控股股份有限公司</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>ssd@coreintelligence.com.tw</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>四維航業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>https://www.swnav.com.tw/sustainability/esg/download</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>行政管理部</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>esg@swnav.com.tw</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>+886-2-8712-1888 ext. 225</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>台塑勝高科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>https://www.fstech.com.tw/FPC_Fstech_Web/fst_csr.html?page=pills-resource&amp;1787629749859#pills-resource</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>永續報告書編製小組</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>蕭</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>蕭先生</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>info@fstech.com.tw</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>02-27122211 ext:6111</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>聲寶股份有限公司</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>https://www.sampo.com.tw/aboutlist.aspx?q=31</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>davechen@sampo.com.tw</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>03-3975151 #1535</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>強茂股份有限公司</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>https://www.panjit.com.tw/tw/Esg/ESG_REPORT_DOWNLOAD/ESG_REPORT</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>ESG專案辦公室</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>黃</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>黃先生</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>supervisor@panjit.com.tw</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>07-621-3121 分機 1213</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>菱生精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>https://www.lingsen.com.tw/webc/html/csr/CSR-Report.aspx</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>rubyhuang@lingsen.com.tw</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>長榮航太科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>https://www.egat.com.tw/documents/2025_EGAT_ESG_Report_CN.pdf</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>egatesg@egat.com.tw</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>03-3519475</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>遠雄自貿港投資控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>https://www.ftz.com.tw/esg/report/</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>ESG永續發展推動委員會</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>莊</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>莊麗琪</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>claire.chuang@ftz.com.tw</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>03-399-2888 # 15521</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>國賓大飯店股份有限公司</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>https://investor.ambassador-hotels.com/stakeholder.htm</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>永續發展處</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>ambcsr@ambassador-hotels.com</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>(02)2100-2100 分機 2120</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>台灣光罩股份有限公司</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>https://www.tmcnet.com.tw/tw/Sustainable/ESGHighlights</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>集團環安工程處</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>esg_tmc@tmcnet.com.tw</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>03-5634370</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>名軒開發股份有限公司</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>https://www.advancetek.com.tw/investor/esg_report/</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>ling@advancetek.com.tw</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>京城建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>https://www.kingtown.com.tw/06.php?A_1=%E5%85%AC%E5%8F%B8%E6%B2%BB%E7%90%86</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>公司治理部</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>bruce@kingtown.com.tw</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>+886-7-558-6368 分機214</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>聯茂電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>https://www.iteqcorp.com/esg/</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>公司治理及永續委員會</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>副理</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>陳副理</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>esg@iteqcorp.com</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>(03)588-7888 分機 8803</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>第一伸銅科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>https://www.fcht.com.tw/index.php?option=module&amp;lang=cht&amp;task=pageinfo&amp;id=271&amp;index=3</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>fl910@hegroup.com.tw</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>台光電子材料股份有限公司</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>https://www.emctw.com/zh-TW/csr_report/index</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>dinah.tai@mail.emctw.com</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>上銀科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>https://esg.hiwin.tw/uploadfiles/file/HIWIN_2025_ESG-C.pdf</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>esg@hiwin.tw</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>昇陽建設企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>https://www.sunty.com.tw/suntyESG/report.html</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>ESG永續專案小組</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>news@sunty.com.tw</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>02-27771355 轉 1507</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>國碩科技工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>http://www.gigastorage.com.tw</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>特別助理</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>曾</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>曾國暉</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>brian@gigastorage.com.tw</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>886-3-598-5510 #5301</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>唐榮鐵工廠股份有限公司</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>https://www.tangeng.com.tw/csr/ov/dow.html</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>企劃處</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>tecsr@mail.tangeng.com.tw</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>(07)802-2811 分機 1551、1556、1557</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>台灣晶技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>https://esg.txccorp.com/esg/sustainability-report/sustainability-report/</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>管理中心</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>esg@txc.com.tw</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>+886-3-469-8121</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>堤維西交通工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>https://www.tyc.com.tw/sustainable</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>行政管理處</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>csr_tyc@tyc.com.tw</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>886-6-265-8781</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>福壽實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>https://esg.fwusow.com.tw/download.php?lang=tw&amp;tb=1&amp;cid=-1</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>fwusow@fwusow.com.tw</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>佳能企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>https://www.abilitytw.com/file/ability-esg-report-2025-c-pdf</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>營運中心</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>協理</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>李</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>李進江</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>esg@abilitytw.com</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>+886-2-8522-9788</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GIS Holding Limited</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>https://esg.gis-touch.com/GIS_ESG/Operation/DownloadZone</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>永續發展委員會ESG工作小組</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>陳小姐</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>esg@gis-touch.com</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>+886 37 777 939 ext.71821</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>聚亨企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>https://www.tycons.com.tw/index.php?option=module&amp;lang=cht&amp;task=pageinfo&amp;id=55&amp;index=1</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>supervisor@mail.tycons.com.tw</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>宏普建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>https://www.hong-pu.com.tw/tw/esg/report</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>永續發展小組</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>劉</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>劉寶姝</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>amy@hong-pu.com.tw</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>(02)2755-2662 #202</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>友勁科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>https://www.cameo.com.tw/wp-content/uploads/2026/08/%E5%8F%8B%E5%8B%81%E7%A7%91%E6%8A%802025%E6%B0%B8%E7%BA%8C%E5%A0%B1%E5%91%8A%E6%9B%B80819FINAL.pdf</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>esg@cameo.com.tw</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>02-7736-3636</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>建漢科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>https://esg.cybertan.com.tw/development/development-02/</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>allen.hu@cybertan.com.tw</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>高端疫苗生物製劑股份有限公司</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>https://www.medigenvac.com/shareholder_info.php</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>管理部</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t>info@medigenvac.com</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>+886-3-668-4866</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>鈺創科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>https://etron.com/zh-hant/esg/sustainability-esg-report-download/</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
         <is>
           <t>esg@etron.com.tw</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>03-5782345 分機:8111</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>東森國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>https://csr.emic.com.tw/report.php</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>投資人關係室</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>協理</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>蔡</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>蔡芸芸</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>vivian_tsai@emg.com.tw</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>+886 2-2755-7565 分機:892</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>愛地雅工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>https://www.idealbike.com.tw/about_tw.php?id=17</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>ESG小組</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>副總經理</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>賴</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>賴名美</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>spokesperson@idealbike.com.tw</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>04-26393242</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>三發地產股份有限公司</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>https://www.sanfar.com.tw/zh-TW/esg#report</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
         <is>
           <t>協理</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>詹</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>詹博全</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>contact@sanfar.com.tw</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>(02)2570-9988</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>威剛科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>https://esg.adata.com/tw/</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>adata@adata.com</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>02-8228-0886</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>威致鋼鐵工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>http://www.weichih.com.tw/spic6.php</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>廠務處</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>處長</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>沈</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>沈宏哲</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>shj96012@weichih.com.tw</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>06-5790213</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>新美齊股份有限公司</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>https://www.jean.com.tw/webapi/77645ee1-6f0a-4546-82a1-6811d9938b24</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
         <is>
           <t>董事長</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>林</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>林傳捷</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>contact@jean.com.tw</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>台郡科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>https://www.flexium.com.tw/Sustainability/ESGOverview?lang=zh-tw</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
         <is>
           <t>ir@flexium.com.tw</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>中國電器股份有限公司</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>www.chinaelectric.com.tw</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>永續發展小組</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
         <is>
           <t>eservice@toa.com.tw</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>02-27191188 分機2210</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>仲琦科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>https://www.hitrontech.com/zh-tw/esg/</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>企業永續發展委員會 永續推行小組</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
         <is>
           <t>csr@hitrontech.com</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>03-578-6658</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>盛餘股份有限公司</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>https://www.shengyusteel.com/FileUpload/susdev/(0828)(%E4%BD%8E%E6%AA%94)%E7%9B%9B%E9%A4%982025%E6%B0%B8%E7%BA%8C%E5%A0%B1%E5%91%8A%E6%9B%B8202608281316001.pdf</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>企業社會責任委員會</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
         <is>
           <t>yx_chen@shengyusteel.com</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>07-8719000 分機:144</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>新光鋼鐵股份有限公司</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>https://csr.hkssteel.com.tw/pdf/2025esg.pdf</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
         <is>
           <t>副總經理</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>劉</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>劉百慧</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>hkssteel@ms4.hinet.net</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>+886-2-2978-8888</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>元大期貨股份有限公司</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>https://www.yuantafutures.com.tw/csr_01</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>綜合企劃部</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
         <is>
           <t>futures@yuanta.com</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>02-2717-6000</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>華固建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>https://www.huaku.com.tw/csrInfo?id=S53wtl21ivWICLmO</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>管理部</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
         <is>
           <t>esg@huaku.com.tw</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>02-2758-2828</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>順天建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>https://www.sweeten.com.tw/interested-parties/</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>葉</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>葉蕙菱</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>sweeten@sweeten.com.tw</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>04-22595777 分機 1107</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>宜進實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>https://www.yijinn.com.tw/our-responsibilities</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
         <is>
           <t>副總經理</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>張</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>張恆嘉</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>albert@yijinn.com.tw</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>(02)26575859 #530</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>新光產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>https://www.skinsurance.com.tw/SKI/Doc.aspx?uID=83.&amp;sID=4723&amp;ST=</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
         <is>
           <t>menghsuan@skinsurance.com.tw</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>欣雄天然氣股份有限公司</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>https://www.shng.com.tw/invment03.html</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>管理部</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>經理</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>吳</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>吳經理</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>management01@shng.com.tw</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>(07)7416101#133</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>長虹建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>https://chonghong.com.tw/esg/esg111</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>總經理室</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
         <is>
           <t>chonghong@chonghong.com.tw</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>02-2396-3280</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>美好證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>https://goodfinance.com/about/esg</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
         <is>
           <t>副總經理</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>陳以白</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>csr@goodfinance.com</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>+886-2-25084888</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>潤弘精密工程事業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>https://www.rtc.com.tw/rtcesg/</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>永續發展推行小組</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
         <is>
           <t>rt007745@mail.ruentex.com.tw</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>(02)-8161-9999 #7444</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>松瑞製藥股份有限公司</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>https://www.saviorlifetec.com.tw/governance/sustainability</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
         <is>
           <t>副總經理</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>林</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>林彥嵐</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>stock@saviorlifetec.com.tw</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>+886-6-5051200 轉1001</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>台康生技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>https://zh-tw.eirgenix.com/esg-esg-overview</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
         <is>
           <t>ir@eirgenix.com</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>(03) 620-5088-2</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>大華金屬工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>https://www.greatchina.com.tw/sustainability-report/</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>姜</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>姜佳君</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>jessie@greatchina.com.tw</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>02-29015153</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>中磊電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>https://www.sercomm.com/tw/sustainability/5</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>企業永續發展委員會永續推行小組</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
         <is>
           <t>esg@sercomm.com</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>+886-2-2655-3988 #2462</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>義隆電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>https://www.emc.com.tw/emc/tw/csr/report</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>人力績效管理部</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>處長</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>李</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>李明霞</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>csr@emc.com.tw</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>+886-3-5639977</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>厚生股份有限公司</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>http://www.frg.com.tw/m/st-esg.html</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>徐</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>徐國倫</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>1101@frgco.com.tw</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>03-4893456</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>喬山健康科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>https://www.johnsonfitness.com.tw/mod/news/index.php?REQUEST_ID=6f11269c4fa89f16dcaaf298183d8b2410f53a76cc4dac8b7f47b51f1849c4f1</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>永續辦公室</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
         <is>
           <t>esg@johnsonfitness.com</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>+886-4-25667100</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>和成欣業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>https://www.hcg.com.tw/tw/esg/esg_report</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>羅</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>羅月英</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>monica@hcgnet.com.tw</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>(03)3623105</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>春雨工廠股份有限公司</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>https://www.chunyu.com.tw/report-download/</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
         <is>
           <t>esg@chunyu.com.tw</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>(07) 622-4111</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>第一產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>https://www.firstins.com.tw/about/csr/csr-index</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>王</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>王景弘</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>tedwang@firstins.com.tw</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>(02)2391-3271 #2506</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>鼎元光電科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>https://www.tyntek.com.tw/sustainability.php?cs=62&amp;sn=63</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>彭</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>彭小姐</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>mish_peng@serv.tyntek.com.tw</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>037-582997 #15200</t>
         </is>
@@ -2443,426 +2814,506 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>聯上開發股份有限公司</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>www.5v.com.tw</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
         <is>
           <t>副總經理</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>曾</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>曾金卿</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>3430@5v.com.tw</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>02-27229898 分機 211</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>正道工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>https://www.rightway.com.tw/userfiles/%E6%AD%A3%E9%81%93%E5%B7%A5%E6%A5%AD_2025%E5%B9%B4%E6%B0%B8%E7%BA%8C%E5%A0%B1%E5%91%8A%E6%9B%B8.pdf</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
         <is>
           <t>don.huang@rightway.tw</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>886-6-2664101</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>勝一化工股份有限公司</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>https://www.shinychem.com.tw/zh-tw/html/sustainableFile</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>企業永續發展委員會秘書室</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
         <is>
           <t>csr@shinychem.com.tw</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>07-6219171</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>裕隆日產汽車股份有限公司</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>https://new.nissan.com.tw/nissan/home/download?pp=financial&amp;f=csr-2025.pdf</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
         <is>
           <t>y.lin@yulon-nissan.com.tw</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>(037) 875881 分機 1630</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>聯華食品工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>https://esg.lianhwa.com.tw/report-download/</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>人才發展部</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>古</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>古翠雲</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>esg@lianhwa.com.tw</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>(02)2552-1666 ext.1751</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>晶豪科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>https://www.esmt.com.tw/download/0826082716oh124576?open=1</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
         <is>
           <t>esg@esmt.com.tw</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>886-3-5781970 分機 2120</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>台灣百和工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>https://esg.paiho.com/esg_report/FY25/</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>永續發展組</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
         <is>
           <t>esg@paiho.com</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>+886-4-756-5307分機199</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>宏全國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>https://esg.honchuan.com/tw/interaction/download/esg-report</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>永續發展部</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
         <is>
           <t>esg@mail.honchuan.com.tw</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>+886-4-23590088 Ext.3103</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>三星科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>https://www.sanshing.com.tw/company7.html</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr">
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>許</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>許春宵</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>sws@mail.sanshing.com.tw</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>06-2306611 ext.252</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>台灣卜蜂企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>https://www.cptwn.com.tw/ec99/rwd1785/category.asp?category_id=27</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>永續發展小組專案管理</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>經理</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>葉</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>葉豪軒</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>ansonye@cptwn.com.tw</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>02-2507-7071</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>億豐綜合工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>https://www.nienmade.com.tw/ESG.aspx</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
         <is>
           <t>jane.wang@nienmade.com.tw</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>台灣表面黏著科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>https://www.tsmt.com/corporate-social-responsibility</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
         <is>
           <t>fenni_chiang@tsmt.com</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>伍豐科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>https://www.fecpos.com/tw/msg/message-301.html?lg=T</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr">
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>賴</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>賴盈甫</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>yingfu.lai@firich.com.tw</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>(02) 2698-1446</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>台燿科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>https://www.tuc.com.tw/zh-tw/corporate/id/153</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>公司治理室</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
         <is>
           <t>ian.huang@tuc.com.tw</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>035551103分機:116</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>嘉晶電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>https://www.epi.episil.com/Default/Sustainability_Report</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
         <is>
           <t>epi.esg@epi.episil.com</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>(03)563-2255</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>日電貿股份有限公司</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>https://www.ndb.com.tw/公司治理/永續報告書/</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr">
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
         <is>
           <t>副總經理</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>侯</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>侯錦華</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>esg@ndb-group.com</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>+886-2-2219-0505</t>
         </is>
@@ -2871,82 +3322,102 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>連展投資控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>www.acon-holding.com</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>永續發展辦公室</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
         <is>
           <t>esg@acon-holding.com</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>(02)2917-5598 #1306</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>建準電機工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>https://esg.sunon.com/esg/reports-download/esg-reports/#content</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
         <is>
           <t>sunonesg@sunon.com</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>彰源企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>https://www.froch.com.tw/TCHI/Corporate_Social_Responsibility_永續報告書下載.html</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
         <is>
           <t>governance@froch.com</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>達方電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>https://esg.darfon.com.tw/</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>永續單位</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
         <is>
           <t>integrity@darfon.com</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>(03)250-8800</t>
         </is>
@@ -2955,1029 +3426,1224 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>亞洲光學股份有限公司</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>www.asia-optical.com</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>企業永續委員會</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>張</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>張士駿</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>esg@aoci.com.tw</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>04-25342550-1700</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>儒鴻企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>https://www.eclat.com.tw/zh-tw/sustainability/metrics-reports/download-reports/</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
         <is>
           <t>eclat-sustainability@eclat.com.tw</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>+886-2-2299-6000</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>普安科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>https://www.infortrend.com/tw/about/report-download</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>永續發展推動中心－企業發展小組</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
         <is>
           <t>esgreport@infortrend.com</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>02-22260126</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>中裕新藥股份有限公司</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>https://www.taimedbiologics.com/article.php?lang=tw&amp;tb=7&amp;cid=412</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
         <is>
           <t>iho@taimedbio.com</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>精材科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>https://www.xintec.com.tw/chi/Legal/ESG_Policy_Reports.html</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
         <is>
           <t>esg@xintec.com.tw</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>+886-3-4331818</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>志超科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>https://www.tpt-pcb.com.tw/pdf/ESG/tpt2025ESGreport.pdf</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
         <is>
           <t>esg@tpt-pcb.com.tw</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>達欣工程股份有限公司</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>https://www.dacin.com.tw/csr/</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>ESG推動小組</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
         <is>
           <t>100104@dacin.com.tw</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>(02)2706-2929 分機 737</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>宏璟建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>https://mis281.wixsite.com/asehcc/system</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
         <is>
           <t>service@asehome.com</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>台灣三洋電機股份有限公司</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>https://www.sanyo.com.tw/company02-5</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>永續發展工作推動小組</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>黃</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>黃安生</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>san0001@sanyo.com.tw</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>02-2521-0251 #1205</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>聯發紡織纖維股份有限公司</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>http://main.lanfa.com.tw/</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr">
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
         <is>
           <t>總經理</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>王</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>王豐岳</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>tpe_hr@lanfa.com.tw</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>(02)2552-1255</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>亞洲塑膠再生資源控股有限公司</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>http://asia-recycle.com/governance/responsibility/</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
         <is>
           <t>weimin831@gmail.com</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>永豐餘消費品實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>https://www.yfycpg.com/zh-TW/esg/report</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>永續辦公室</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>資深總監</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>歐</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>歐玉翬</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>cpg.esg@yfycpg.com</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>(02) 2192-1022</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>美亞鋼管廠股份有限公司</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>https://www.mayer.com.tw/zh-tw/governance_10</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr">
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
         <is>
           <t>協理</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>陳叔永</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>jeffery.chen@mayergroup.com.tw</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>(02)2509-1199 分機 2118</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>美時化學製藥股份有限公司</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>https://api.lotuspharm.com/storage/esg-reports/%E7%BE%8E%E6%99%82%E8%A3%BD%E8%97%A5_2025%E6%B0%B8%E7%BA%8C%E5%A0%B1%E5%91%8A%E6%9B%B8.pdf</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>公司治理處</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
         <is>
           <t>investor@lotuspharm.com</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>+886-2-27005908</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>泰福生技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>https://www.tanvex.com/investor-c.php</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>永續推動工作小組</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
         <is>
           <t>contact@tanvex.com</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>+886-3-658-3899</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>富邦媒體科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>https://corp.momo.com.tw/file/csr/csrReport/momo_2025ESGreport.pdf</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>財會處 永續發展部</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
         <is>
           <t>esg@fmt.com.tw</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>+886 2 2162 6688 ext. 1231</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>泰鼎國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>https://www.apex-intl.com.tw/esg/reports</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>永續發展暨提名委員會</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
         <is>
           <t>csr@apex-intl.com.tw</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>(02) 2717-0032</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>如興股份有限公司</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>https://roohsinggroup.com/zh-tw/social_report.php</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>財會管理中心</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
         <is>
           <t>roohsing@tw.roohsing.com</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>豐藝電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>https://www.promate.com.tw/esg/esg-report/</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>董事長室</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>林</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>林先生</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>noah_lim@promate.com.tw</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>+886-2-2659-0303 #1205</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>智原科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>https://www.faraday-tech.com/resources/PDFFile/CSR/Faraday_ESG_Report_2025.pdf</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>企業永續委員會</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>王</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>王維鼎</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>esg@faraday-tech.com</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>886-3-5787888 分機 84064</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>廣運機械工程股份有限公司</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>https://www.kenmec.com/tw/investor06-7.aspx</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
         <is>
           <t>kenmec@kenmec.com</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>神腦國際企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>https://www.senao.com.tw/pages/esg_governance</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>ESG秘書處</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>管理師</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>陳怡璇</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>sandra.chen@senao.com.tw</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>(02)2218-3588</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>東台精機股份有限公司</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>https://www.tongtaimachinetool.com/</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>永續治理辦公室</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>經理</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>嚴</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>嚴琳</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>esg@tongtai.com.tw</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>07-9761588 #8006</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>大展證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>https://www.tachan.com.tw/corpgovernance?func=SocResp&amp;page=SocResp_1&amp;item=SocResp_1_12</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
         <is>
           <t>service@mail.tachan.com.tw</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>(02)2555-1234</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>來億興業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>https://www.laiyih.com/sustainability-report</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>永續發展部</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
         <is>
           <t>laiyihesg@laiyih.com.tw</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>群益期貨股份有限公司</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>https://www.capitalfutures.com.tw/zh-tw/esg/sustainability</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
         <is>
           <t>moma.lin@futures.capital.com.tw</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>+8862 2700 2888</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>東南實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>https://www.sesoda.com.tw/csr</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
         <is>
           <t>sesodaesg@sesoda.com.tw</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>02-2704-7272</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>中聯資源股份有限公司</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>https://www.chc.com.tw/csr/index.html</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>管理處</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
         <is>
           <t>mservice@chc.com.tw</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>07-9736668</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>國統國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>https://www.kti.com.tw/list/cate-376641.htm</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
         <is>
           <t>ir@kti.com.tw</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>07-5573755</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>世紀鋼鐵結構股份有限公司</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>https://www.century.com.tw/tw/duty/50/</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr">
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
         <is>
           <t>協理</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>李</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>李協理</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>jack.lee@century.com.tw</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>永崴投資控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>https://www.fit-holding.com/report/</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr">
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>林</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>林小姐</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>stakeholders@fit-holding.com</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>02-2269-9866</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>友霖生技醫藥股份有限公司</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>https://www.oppharma.com/zh-TW/blogs/investor_relations/sustainability-report</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
         <is>
           <t>op@oppharma.com</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>02-23257621</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>味王股份有限公司</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>https://www.vewong.com/ec99/ushop20069/profile-12.asp</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>永續發展執行委員會推動小組</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>經理</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>陳榮顯</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>niel@vewong.com.tw</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>(02)2571-7271 # 825</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>中鋼碳素化學股份有限公司</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>https://www.cscc.com.tw/csr/csr/abo.html</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>管理處企劃課</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
         <is>
           <t>02886@e-cscc.com.tw</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>(07)3383515#39273</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>大眾全球投資控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>https://www.ficg.com.tw/wp-content/uploads/2026/08/FICG_2025ESG_fin_web_C_v2.pdf.pdf</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>永續發展辦公室</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
         <is>
           <t>ficg_esg@fic.com.tw</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>02-8751-8751 #6399、#7352</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>德律科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>https://www.tri.com.tw/tw/investor/investor_detail-173-2-3--2040-1.html</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>ESG報告書編輯小組</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
         <is>
           <t>ir@tri.com.tw</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>+886-2-28328918</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>震旦行股份有限公司</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>https://www.aurora.com.tw/esg-result</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr">
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>蔡</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>蔡翔州</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>ir@aurora.com.tw</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>02-2345-8088</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>全科科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>https://www.alltek.com/%E4%BC%81%E6%A5%AD%E6%B0%B8%E7%BA%8C/%E4%BA%92%E5%8B%95%E5%B0%88%E5%8D%80/%E6%B0%B8%E7%BA%8C%E5%A0%B1%E5%91%8A%E6%9B%B8%E4%B8%8B%E8%BC%89/</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
         <is>
           <t>esg@alltek.com</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>一詮精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>https://www.i-chiun.com.tw/ec99/rwd1809/category.asp?category_id=38</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
         <is>
           <t>pure@i-chiun.com.tw</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>02-2299-0001</t>
         </is>
@@ -3986,937 +4652,1112 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>南緯實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>www.texray.com</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>專案管理</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
         <is>
           <t>tr-hq@texray.com</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>(02)2521-5155</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>精剛精密科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>https://www.s-tech.com.tw/zh-tw/a4-694-6019/5-%E6%B0%B8%E7%BA%8C%E5%A0%B1%E5%91%8A%E6%9B%B8.html</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>ESG報告書編輯小組</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
         <is>
           <t>stc_supervisor@s-tech.com.tw</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>(06)6235143</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>聯上實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>http://kh.vvvvv.com.tw/kh/p4-2-12.asp</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
         <is>
           <t>nancy@vvvvv.com.tw</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>巧新科技工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>https://www.superalloy.tw/sustainability/</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
         <is>
           <t>admin@superalloy.tw</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>05-5512288</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>盛群半導體股份有限公司</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>https://www.holtek.com.tw/page/about_holtek/responsibility/sustainability</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr">
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>陳林政</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>ir@holtek.com.tw</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>+886-3-563-1999 分機 3573</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>系統電子工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>https://www.sysgration.com/zh-tw/esg-report-ch</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
         <is>
           <t>esgteam@sysgration.com</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>新亞建設開發股份有限公司</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>https://www.newasia.com.tw/company/esg</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
         <is>
           <t>yuan@newasia.com.tw</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>正達國際光電股份有限公司</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>http://www.gtoc.com.tw/webc/html/csr/06.aspx</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
         <is>
           <t>esg@gtoc.com.tw</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>太極能源科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>https://www.tainergy.com/esg/4</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
         <is>
           <t>beauty.yu@tainergy.com</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>訊舟科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>https://download.edimax.com/mw/cufiles/files/investor/sustainable_development/2025_Edimax_ESG_report.pdf</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
         <is>
           <t>協理</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>廖</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>廖若穎</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>ir@edimax.com.tw</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>全坤建設開發股份有限公司</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>https://www.gtg.com.tw/page/investment/pages.aspx?kind=32&amp;da=n8</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr">
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>洪</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>洪小慧</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>hhh@mail.gtg.com.tw</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>02-87918888 分機 271</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>旺旺友聯產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>https://www.wwunion.com/?p=16085</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>行銷企劃部</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>翁</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>翁尚怡</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>sunny.weng@wwunion.com</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="H145" t="inlineStr">
         <is>
           <t>02-2776-5567</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>全家便利商店股份有限公司</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>https://www.family.com.tw/ESG/report-pdf/2025_%e6%b0%b8%e7%ba%8c%e5%a0%b1%e5%91%8a%e6%9b%b8.pdf</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>公司治理暨企劃Team</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>襄理</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>潘</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>潘襄理</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>ginnypan@family.com.tw</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>(02)2523-9588</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>敦泰電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>https://www.focaltech-electronics.com/zh-TW/download/index</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr">
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>李</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>李佳縈</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>joy.lee@focaltech-electronics.com</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>台灣櫻花股份有限公司</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>https://www.sakura.com.tw/SustainableReport</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>經營規劃室</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
         <is>
           <t>service@sakura.com.tw</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>04-2566-6106</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>昆盈企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>https://www.geniusnet.com/tw/esg/sustainability</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>財會處</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>副總經理</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>高安民</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>kyecsr@geniusnet.com.tw</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>(02)2995-6645 ext.3282</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>斐成開發科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>https://fce.com.tw/uploads/pdf/20260828_164225_HlBfd.pdf</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>韓</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>韓元翔</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>fce_contact@yahoo.com</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>06 299-5586</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>群聯電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>https://www.phison.com/wp-content/uploads/2026/08/2025-Phison-ESG-Report-TC-2.pdf</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>市場暨專案企劃部</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>陳小姐</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>peiwen_chen@phison.com</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>+886-37-586896</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>智易科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>https://csr.arcadyan.com/zh-hant/resources/reports/</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>永續發展辦公室</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
         <is>
           <t>csr@arcadyan.com</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>+886 3 572 7000</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>利奇機械工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>http://www.leechi.com.tw</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
         <is>
           <t>saleechi@leechi.com.tw</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>(04)7382121</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>隆大營建事業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>https://www.longda.com.tw/csr-list.php?id=895</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>管理部</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>高莉庭</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>ninikao@longda.com.tw</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>07-336-7041 分機 303</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>恒耀國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>https://www.qst.com.tw/cht/Investors_7.aspx</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>物流管理部</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>協理</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>應</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>應金娟</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>qstmail@qst.com.tw</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>+886 6 2081997 #11800</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>福貞控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>http://tw.kingcan.net/wp-content/uploads/2026/08/%E7%A6%8F%E8%B2%9E%E6%8E%A7%E8%82%A1-2025ESG(CH).pdf</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>ESG永續發展委員會</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
         <is>
           <t>spokesman@kchld.com</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>鉅祥企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>https://www.gshank.info/tw/csr</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>總務部</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>陳裕祥</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>second@mail.gs.com.tw</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="H157" t="inlineStr">
         <is>
           <t>03-4775141 分機 228</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>永信建設開發股份有限公司</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>https://www.ys-construction.com.tw/download#d3</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>ESG小組</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
         <is>
           <t>ysesg@yungshin.com.tw</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>(07) 222-9460#16</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>盟立自動化股份有限公司</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>https://www.mirle.com.tw/esg/document/</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr">
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
         <is>
           <t>財務長</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>林</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>林芳毅</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>esg@mirle.com.tw</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>永笙生技股份有限公司</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
         <is>
           <t>investors@stemcytebio.com</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>越峰電子材料股份有限公司</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>https://www.usig.com/ACMECSR/Report.aspx</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>ESG委員會</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>彭</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>彭文忠</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>kevinpp@usig.com</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>(886-3)4837238</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>亞洲航空股份有限公司</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>https://www.airasia.com.tw/index.php?option=module&amp;lang=cht&amp;task=showlist&amp;id=455&amp;index=1</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>永續推行小組</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
         <is>
           <t>ir@airasia.com.tw</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>06-2681911#2005</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>高林實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>https://www.collins.com.tw/pages/39/%E6%B0%B8%E7%BA%8C%E5%A0%B1%E5%91%8A%E6%9B%B8/%E6%B0%B8%E7%BA%8C%E5%A0%B1%E5%91%8A</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>公司治理課</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr">
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
         <is>
           <t>esg@collins.com.tw</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>(02) 2712-5311 #300</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>同欣電子工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>https://www.theil.com/zh-tw/csr_report.php</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>永續辦公室</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr">
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
         <is>
           <t>esg@theil.com</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="H164" t="inlineStr">
         <is>
           <t>03-5535888</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>聯嘉光電投資控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>https://www.eoi.com.tw/PDFs/ESG/2025-EOI-Sustainability-Report-c.pdf</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>永續發展委員會</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr">
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
         <is>
           <t>csr@eoi.com.tw</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>+886-37-539000 EXT:11010</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>光譜電工股份有限公司</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>https://spe-group.com.tw/</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr">
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
         <is>
           <t>becky_tseng@spe-group.com.tw</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>永昕生物醫藥股份有限公司</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>https://www.mycenax.com/csr.php?lang=tw</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr">
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
         <is>
           <t>ir_esg@mycenax.com</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="H167" t="inlineStr">
         <is>
           <t>(02) 26558951</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>全友電腦股份有限公司</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>https://microtek.com/uploads/f4ac2426817d4e2c3a288c891f4d90ab.pdf</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
-      <c r="C168" t="inlineStr">
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
         <is>
           <t>副總經理</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="E168" t="inlineStr">
         <is>
           <t>戴</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>戴輝權</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t>chuan.tai@microtek.com.tw</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="H168" t="inlineStr">
         <is>
           <t>03-577-2155 分機338</t>
         </is>
@@ -4925,276 +5766,326 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t>廣積科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
           <t>www.ibase.com.tw/uploads/images/esg/IBASE_2025_ESG_Report_TC.pdf</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>ESG專案負責小組</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>張</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>張學麟</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>sam_chang@ibase.com.tw</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>(02)2655-7588</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>晟銘電子科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>https://www.uneec.com/tw/responsibility</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
         <is>
           <t>service@tw.uneec.com</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>網路家庭國際資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>https://corp.pchome.tw/corporate-social-responsibility/esg%E5%A0%B1%E5%91%8A%E6%9B%B8/</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>公共關係室 公共事務科</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr">
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
         <is>
           <t>gr@staff.pchome.com.tw</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="H171" t="inlineStr">
         <is>
           <t>+886-2-2700-0898</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>新鉅科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>https://www.newmax.com.tw/esg.html</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr">
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
         <is>
           <t>chi.chang@newmax.com.tw</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>勤益投資控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>https://www.gtm.com.tw/esg/#Report</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr">
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>馮</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>馮于珍</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>gtm@gtm.com.tw</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>立德電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>https://www.lei.com.tw/tw/responsibility/report.aspx</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>永續辦公室</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>小姐</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>朱</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>朱品貞</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>esg@l-e-i.com</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>+886-2-8195-3058 #8273</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>開曼東明控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>https://www.tonggroup.com.tw/sustainability</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>ESG委員會</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr">
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
         <is>
           <t>ir@tonggroup.com.tw</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="H175" t="inlineStr">
         <is>
           <t>886-7-6235538</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>鈺齊國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>https://www.fulgentsun.com/respon06.asp</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
         <is>
           <t>zoe.she@fulgentsun.com</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>志強國際企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>https://www.sportsgear.com.tw/ESG.html</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>董事會秘書室</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>先生</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>古</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>古富昇</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>fusheng.ku@spg-sportsgear.com</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>(886)4-2258-5388</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>臺鹽實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>https://www.tybio.com.tw/taiyen/tw/csr/1/report</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>品牌行銷處</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>處長</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>陳</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>陳美文</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>tsi201@tybio.com.tw</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="H178" t="inlineStr">
         <is>
           <t>+886-6-2160688</t>
         </is>
@@ -5202,175 +6093,175 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B177" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
